--- a/Aprūpes lapas.xlsx
+++ b/Aprūpes lapas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Pašaprūpes spēju novērtējums" sheetId="1" state="visible" r:id="rId3"/>
@@ -1022,7 +1022,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="74">
   <si>
     <t xml:space="preserve">Sociālā atbalsta centrs "Vaiņode"</t>
   </si>
@@ -1343,6 +1343,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">38.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Higiēna</t>
   </si>
   <si>
@@ -1632,6 +1635,7 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -1759,129 +1763,137 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2076,421 +2088,421 @@
   <dimension ref="A1:N23"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6" t="n">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="M7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" s="7" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4"/>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2522,1229 +2534,1231 @@
   <dimension ref="A1:AF1048576"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="5.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="3" style="11" width="4.14"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="11" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="5.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="3" style="12" width="4.14"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="12" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="14"/>
+      <c r="Z4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="17" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="15"/>
-      <c r="Z5" s="15"/>
-      <c r="AA5" s="15"/>
-      <c r="AB5" s="15"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="32.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="18"/>
-      <c r="AC6" s="18"/>
-      <c r="AD6" s="18"/>
-      <c r="AE6" s="18"/>
-      <c r="AF6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="20" t="s">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
-      <c r="V7" s="21"/>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="21"/>
-      <c r="AD7" s="21"/>
-      <c r="AE7" s="21"/>
-      <c r="AF7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="22"/>
+      <c r="AE7" s="22"/>
+      <c r="AF7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23" t="n">
+      <c r="B8" s="23"/>
+      <c r="C8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23" t="n">
+      <c r="D8" s="24"/>
+      <c r="E8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23" t="n">
+      <c r="F8" s="24"/>
+      <c r="G8" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23" t="n">
+      <c r="H8" s="24"/>
+      <c r="I8" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="24" t="n">
+      <c r="J8" s="24"/>
+      <c r="K8" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24" t="n">
+      <c r="L8" s="25"/>
+      <c r="M8" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="23" t="n">
+      <c r="N8" s="25"/>
+      <c r="O8" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23" t="n">
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23" t="n">
+      <c r="R8" s="24"/>
+      <c r="S8" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23" t="n">
+      <c r="T8" s="24"/>
+      <c r="U8" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23" t="n">
+      <c r="V8" s="24"/>
+      <c r="W8" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23" t="n">
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23" t="n">
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24" t="n">
         <v>13</v>
       </c>
-      <c r="AB8" s="23"/>
-      <c r="AC8" s="23" t="n">
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="AD8" s="23"/>
-      <c r="AE8" s="23" t="n">
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="AF8" s="23"/>
+      <c r="AF8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="24" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="M9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="N9" s="24" t="s">
+      <c r="N9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="O9" s="24" t="s">
+      <c r="O9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="P9" s="24" t="s">
+      <c r="P9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="Q9" s="24" t="s">
+      <c r="Q9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="R9" s="24" t="s">
+      <c r="R9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="S9" s="24" t="s">
+      <c r="S9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="24" t="s">
+      <c r="T9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="24" t="s">
+      <c r="U9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="V9" s="24" t="s">
+      <c r="V9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="W9" s="24" t="s">
+      <c r="W9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="X9" s="24" t="s">
+      <c r="X9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="Y9" s="24" t="s">
+      <c r="Y9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="Z9" s="24" t="s">
+      <c r="Z9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="AA9" s="24" t="s">
+      <c r="AA9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="AB9" s="24" t="s">
+      <c r="AB9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="AC9" s="24" t="s">
+      <c r="AC9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="AD9" s="24" t="s">
+      <c r="AD9" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="AE9" s="24" t="s">
+      <c r="AE9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="AF9" s="24" t="s">
+      <c r="AF9" s="25" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="26"/>
-      <c r="AB10" s="26"/>
-      <c r="AC10" s="26"/>
-      <c r="AD10" s="26"/>
-      <c r="AE10" s="26"/>
-      <c r="AF10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27"/>
+      <c r="AB10" s="27"/>
+      <c r="AC10" s="27"/>
+      <c r="AD10" s="27"/>
+      <c r="AE10" s="27"/>
+      <c r="AF10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="28" t="s">
+      <c r="A11" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="24"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="24"/>
-      <c r="AA11" s="24"/>
-      <c r="AB11" s="24"/>
-      <c r="AC11" s="24"/>
-      <c r="AD11" s="24"/>
-      <c r="AE11" s="24"/>
-      <c r="AF11" s="24"/>
+      <c r="B11" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="24"/>
-      <c r="AA12" s="24"/>
-      <c r="AB12" s="24"/>
-      <c r="AC12" s="24"/>
-      <c r="AD12" s="24"/>
-      <c r="AE12" s="24"/>
-      <c r="AF12" s="24"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="25"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="25"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="25"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="25"/>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="28" t="s">
+      <c r="A18" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="24"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
-      <c r="AC18" s="24"/>
-      <c r="AD18" s="24"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="24"/>
+      <c r="B18" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
+      <c r="W18" s="25"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="24"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="24"/>
-      <c r="AA19" s="24"/>
-      <c r="AB19" s="24"/>
-      <c r="AC19" s="24"/>
-      <c r="AD19" s="24"/>
-      <c r="AE19" s="24"/>
-      <c r="AF19" s="24"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="25"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="28" t="s">
+      <c r="A21" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
+      <c r="B21" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="24"/>
-      <c r="AA22" s="24"/>
-      <c r="AB22" s="24"/>
-      <c r="AC22" s="24"/>
-      <c r="AD22" s="24"/>
-      <c r="AE22" s="24"/>
-      <c r="AF22" s="24"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="24"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="24"/>
-      <c r="AA23" s="24"/>
-      <c r="AB23" s="24"/>
-      <c r="AC23" s="24"/>
-      <c r="AD23" s="24"/>
-      <c r="AE23" s="24"/>
-      <c r="AF23" s="24"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="24"/>
-      <c r="U24" s="24"/>
-      <c r="V24" s="24"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="24"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="24"/>
-      <c r="AA24" s="24"/>
-      <c r="AB24" s="24"/>
-      <c r="AC24" s="24"/>
-      <c r="AD24" s="24"/>
-      <c r="AE24" s="24"/>
-      <c r="AF24" s="24"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="28" t="s">
+      <c r="A25" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
-      <c r="S25" s="24"/>
-      <c r="T25" s="24"/>
-      <c r="U25" s="24"/>
-      <c r="V25" s="24"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="24"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="24"/>
-      <c r="AC25" s="24"/>
-      <c r="AD25" s="24"/>
-      <c r="AE25" s="24"/>
-      <c r="AF25" s="24"/>
+      <c r="B25" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="27"/>
-      <c r="B26" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
-      <c r="Q26" s="24"/>
-      <c r="R26" s="24"/>
-      <c r="S26" s="24"/>
-      <c r="T26" s="24"/>
-      <c r="U26" s="24"/>
-      <c r="V26" s="24"/>
-      <c r="W26" s="24"/>
-      <c r="X26" s="24"/>
-      <c r="Y26" s="24"/>
-      <c r="Z26" s="24"/>
-      <c r="AA26" s="24"/>
-      <c r="AB26" s="24"/>
-      <c r="AC26" s="24"/>
-      <c r="AD26" s="24"/>
-      <c r="AE26" s="24"/>
-      <c r="AF26" s="24"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="25"/>
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="25"/>
+      <c r="AF26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="24"/>
-      <c r="P27" s="24"/>
-      <c r="Q27" s="24"/>
-      <c r="R27" s="24"/>
-      <c r="S27" s="24"/>
-      <c r="T27" s="24"/>
-      <c r="U27" s="24"/>
-      <c r="V27" s="24"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="24"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="24"/>
-      <c r="AA27" s="24"/>
-      <c r="AB27" s="24"/>
-      <c r="AC27" s="24"/>
-      <c r="AD27" s="24"/>
-      <c r="AE27" s="24"/>
-      <c r="AF27" s="24"/>
+      <c r="A27" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="30"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
+      <c r="AC27" s="25"/>
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="25"/>
+      <c r="AF27" s="25"/>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="24"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="24"/>
-      <c r="AA28" s="24"/>
-      <c r="AB28" s="24"/>
-      <c r="AC28" s="24"/>
-      <c r="AD28" s="24"/>
-      <c r="AE28" s="24"/>
-      <c r="AF28" s="24"/>
+      <c r="A28" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="30"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="25"/>
+      <c r="AF28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="24"/>
-      <c r="V29" s="24"/>
-      <c r="W29" s="24"/>
-      <c r="X29" s="24"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="24"/>
-      <c r="AA29" s="24"/>
-      <c r="AB29" s="24"/>
-      <c r="AC29" s="24"/>
-      <c r="AD29" s="24"/>
-      <c r="AE29" s="24"/>
-      <c r="AF29" s="24"/>
+      <c r="A29" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
+      <c r="W29" s="25"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="25"/>
+      <c r="AA29" s="25"/>
+      <c r="AB29" s="25"/>
+      <c r="AC29" s="25"/>
+      <c r="AD29" s="25"/>
+      <c r="AE29" s="25"/>
+      <c r="AF29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="24"/>
-      <c r="R30" s="24"/>
-      <c r="S30" s="24"/>
-      <c r="T30" s="24"/>
-      <c r="U30" s="24"/>
-      <c r="V30" s="24"/>
-      <c r="W30" s="24"/>
-      <c r="X30" s="24"/>
-      <c r="Y30" s="24"/>
-      <c r="Z30" s="24"/>
-      <c r="AA30" s="24"/>
-      <c r="AB30" s="24"/>
-      <c r="AC30" s="24"/>
-      <c r="AD30" s="24"/>
-      <c r="AE30" s="24"/>
-      <c r="AF30" s="24"/>
+      <c r="A30" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="30"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
+      <c r="W30" s="25"/>
+      <c r="X30" s="25"/>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="25"/>
+      <c r="AA30" s="25"/>
+      <c r="AB30" s="25"/>
+      <c r="AC30" s="25"/>
+      <c r="AD30" s="25"/>
+      <c r="AE30" s="25"/>
+      <c r="AF30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
-      <c r="Q31" s="24"/>
-      <c r="R31" s="24"/>
-      <c r="S31" s="24"/>
-      <c r="T31" s="24"/>
-      <c r="U31" s="24"/>
-      <c r="V31" s="24"/>
-      <c r="W31" s="24"/>
-      <c r="X31" s="24"/>
-      <c r="Y31" s="24"/>
-      <c r="Z31" s="24"/>
-      <c r="AA31" s="24"/>
-      <c r="AB31" s="24"/>
-      <c r="AC31" s="24"/>
-      <c r="AD31" s="24"/>
-      <c r="AE31" s="24"/>
-      <c r="AF31" s="24"/>
+      <c r="A31" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="30"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="25"/>
+      <c r="W31" s="25"/>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="25"/>
+      <c r="Z31" s="25"/>
+      <c r="AA31" s="25"/>
+      <c r="AB31" s="25"/>
+      <c r="AC31" s="25"/>
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="25"/>
+      <c r="AF31" s="25"/>
     </row>
     <row r="32" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="24"/>
-      <c r="Q32" s="24"/>
-      <c r="R32" s="24"/>
-      <c r="S32" s="24"/>
-      <c r="T32" s="24"/>
-      <c r="U32" s="24"/>
-      <c r="V32" s="24"/>
-      <c r="W32" s="24"/>
-      <c r="X32" s="24"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="24"/>
-      <c r="AA32" s="24"/>
-      <c r="AB32" s="24"/>
-      <c r="AC32" s="24"/>
-      <c r="AD32" s="24"/>
-      <c r="AE32" s="24"/>
-      <c r="AF32" s="24"/>
+      <c r="A32" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
+      <c r="AE32" s="32"/>
+      <c r="AF32" s="32"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4019,1100 +4033,1100 @@
   <dimension ref="A1:AH26"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="3" style="0" width="3.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="3" style="1" width="3.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF2" s="25"/>
+      <c r="AG2" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH2" s="24"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="U3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="V3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH3" s="25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+    </row>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="25"/>
+      <c r="AG5" s="25"/>
+      <c r="AH5" s="25"/>
+    </row>
+    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+      <c r="AH6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="25"/>
+      <c r="AH7" s="25"/>
+    </row>
+    <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="25"/>
+      <c r="AH8" s="25"/>
+    </row>
+    <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="25"/>
+    </row>
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28"/>
+      <c r="B10" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="25"/>
+    </row>
+    <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+    </row>
+    <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="25"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="25"/>
+    </row>
+    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
+      <c r="AH13" s="25"/>
+    </row>
+    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="25"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="25"/>
+      <c r="AH14" s="25"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+      <c r="AH15" s="25"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="25"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
+      <c r="W18" s="25"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
+      <c r="AH18" s="25"/>
+    </row>
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="25"/>
+      <c r="AH19" s="25"/>
+    </row>
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="25"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="25"/>
+      <c r="AH20" s="25"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="30"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="25"/>
+      <c r="AH21" s="25"/>
+    </row>
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="25"/>
+    </row>
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="25"/>
+    </row>
+    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="30"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25"/>
+      <c r="AH24" s="25"/>
+    </row>
+    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="30"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="25"/>
+    </row>
+    <row r="26" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z2" s="23"/>
-      <c r="AA2" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB2" s="23"/>
-      <c r="AC2" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD2" s="23"/>
-      <c r="AE2" s="24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="AH2" s="23"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="U3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="V3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="X3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH3" s="24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="26"/>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="26"/>
-      <c r="AH4" s="26"/>
-    </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24"/>
-      <c r="Z5" s="24"/>
-      <c r="AA5" s="24"/>
-      <c r="AB5" s="24"/>
-      <c r="AC5" s="24"/>
-      <c r="AD5" s="24"/>
-      <c r="AE5" s="24"/>
-      <c r="AF5" s="24"/>
-      <c r="AG5" s="24"/>
-      <c r="AH5" s="24"/>
-    </row>
-    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27"/>
-      <c r="B6" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
-      <c r="V6" s="24"/>
-      <c r="W6" s="24"/>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="24"/>
-      <c r="Z6" s="24"/>
-      <c r="AA6" s="24"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="24"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="24"/>
-      <c r="AH6" s="24"/>
-    </row>
-    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27"/>
-      <c r="B7" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="24"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="24"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="24"/>
-      <c r="AH7" s="24"/>
-    </row>
-    <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27"/>
-      <c r="B8" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="24"/>
-      <c r="AH8" s="24"/>
-    </row>
-    <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27"/>
-      <c r="B9" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="24"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="24"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="24"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="24"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="24"/>
-      <c r="AH9" s="24"/>
-    </row>
-    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="24"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="24"/>
-      <c r="AA10" s="24"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="24"/>
-      <c r="AD10" s="24"/>
-      <c r="AE10" s="24"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="24"/>
-      <c r="AH10" s="24"/>
-    </row>
-    <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="24"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="24"/>
-      <c r="AA11" s="24"/>
-      <c r="AB11" s="24"/>
-      <c r="AC11" s="24"/>
-      <c r="AD11" s="24"/>
-      <c r="AE11" s="24"/>
-      <c r="AF11" s="24"/>
-      <c r="AG11" s="24"/>
-      <c r="AH11" s="24"/>
-    </row>
-    <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="24"/>
-      <c r="AA12" s="24"/>
-      <c r="AB12" s="24"/>
-      <c r="AC12" s="24"/>
-      <c r="AD12" s="24"/>
-      <c r="AE12" s="24"/>
-      <c r="AF12" s="24"/>
-      <c r="AG12" s="24"/>
-      <c r="AH12" s="24"/>
-    </row>
-    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="24"/>
-      <c r="AH13" s="24"/>
-    </row>
-    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="24"/>
-      <c r="AH14" s="24"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
-      <c r="AH15" s="24"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="24"/>
-      <c r="AH16" s="24"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="24"/>
-      <c r="AH17" s="24"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="24"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
-      <c r="AC18" s="24"/>
-      <c r="AD18" s="24"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="24"/>
-      <c r="AH18" s="24"/>
-    </row>
-    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="24"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="24"/>
-      <c r="AA19" s="24"/>
-      <c r="AB19" s="24"/>
-      <c r="AC19" s="24"/>
-      <c r="AD19" s="24"/>
-      <c r="AE19" s="24"/>
-      <c r="AF19" s="24"/>
-      <c r="AG19" s="24"/>
-      <c r="AH19" s="24"/>
-    </row>
-    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
-      <c r="AH20" s="24"/>
-    </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="24"/>
-      <c r="AH21" s="24"/>
-    </row>
-    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="24"/>
-      <c r="AA22" s="24"/>
-      <c r="AB22" s="24"/>
-      <c r="AC22" s="24"/>
-      <c r="AD22" s="24"/>
-      <c r="AE22" s="24"/>
-      <c r="AF22" s="24"/>
-      <c r="AG22" s="24"/>
-      <c r="AH22" s="24"/>
-    </row>
-    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="24"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="24"/>
-      <c r="AA23" s="24"/>
-      <c r="AB23" s="24"/>
-      <c r="AC23" s="24"/>
-      <c r="AD23" s="24"/>
-      <c r="AE23" s="24"/>
-      <c r="AF23" s="24"/>
-      <c r="AG23" s="24"/>
-      <c r="AH23" s="24"/>
-    </row>
-    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="24"/>
-      <c r="U24" s="24"/>
-      <c r="V24" s="24"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="24"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="24"/>
-      <c r="AA24" s="24"/>
-      <c r="AB24" s="24"/>
-      <c r="AC24" s="24"/>
-      <c r="AD24" s="24"/>
-      <c r="AE24" s="24"/>
-      <c r="AF24" s="24"/>
-      <c r="AG24" s="24"/>
-      <c r="AH24" s="24"/>
-    </row>
-    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
-      <c r="S25" s="24"/>
-      <c r="T25" s="24"/>
-      <c r="U25" s="24"/>
-      <c r="V25" s="24"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="24"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="24"/>
-      <c r="AC25" s="24"/>
-      <c r="AD25" s="24"/>
-      <c r="AE25" s="24"/>
-      <c r="AF25" s="24"/>
-      <c r="AG25" s="24"/>
-      <c r="AH25" s="24"/>
-    </row>
-    <row r="26" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
-      <c r="Q26" s="24"/>
-      <c r="R26" s="24"/>
-      <c r="S26" s="24"/>
-      <c r="T26" s="24"/>
-      <c r="U26" s="24"/>
-      <c r="V26" s="24"/>
-      <c r="W26" s="24"/>
-      <c r="X26" s="24"/>
-      <c r="Y26" s="24"/>
-      <c r="Z26" s="24"/>
-      <c r="AA26" s="24"/>
-      <c r="AB26" s="24"/>
-      <c r="AC26" s="24"/>
-      <c r="AD26" s="24"/>
-      <c r="AE26" s="24"/>
-      <c r="AF26" s="24"/>
-      <c r="AG26" s="24"/>
-      <c r="AH26" s="24"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="253">

--- a/Aprūpes lapas.xlsx
+++ b/Aprūpes lapas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Pašaprūpes spēju novērtējums" sheetId="1" state="visible" r:id="rId3"/>
@@ -1022,7 +1022,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
   <si>
     <t xml:space="preserve">Sociālā atbalsta centrs "Vaiņode"</t>
   </si>
@@ -1341,9 +1341,6 @@
       </rPr>
       <t xml:space="preserve"> — rakstām sarkani, cik ir. Ja zem 37°C — rakstām N.</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6</t>
   </si>
   <si>
     <t xml:space="preserve">Higiēna</t>
@@ -2927,9 +2924,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="26"/>
-      <c r="C10" s="27" t="s">
-        <v>45</v>
-      </c>
+      <c r="C10" s="27"/>
       <c r="D10" s="27"/>
       <c r="E10" s="27"/>
       <c r="F10" s="27"/>
@@ -2962,10 +2957,10 @@
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="29" t="s">
         <v>46</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>47</v>
       </c>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
@@ -3001,7 +2996,7 @@
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28"/>
       <c r="B12" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -3037,7 +3032,7 @@
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28"/>
       <c r="B13" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
@@ -3073,7 +3068,7 @@
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28"/>
       <c r="B14" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
@@ -3109,7 +3104,7 @@
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28"/>
       <c r="B15" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -3145,7 +3140,7 @@
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28"/>
       <c r="B16" s="29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -3181,7 +3176,7 @@
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="28"/>
       <c r="B17" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
@@ -3216,10 +3211,10 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="29" t="s">
         <v>54</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>55</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
@@ -3255,7 +3250,7 @@
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28"/>
       <c r="B19" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -3291,7 +3286,7 @@
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28"/>
       <c r="B20" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -3326,10 +3321,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="29" t="s">
         <v>58</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>59</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -3365,7 +3360,7 @@
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28"/>
       <c r="B22" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -3401,7 +3396,7 @@
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="28"/>
       <c r="B23" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -3437,7 +3432,7 @@
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28"/>
       <c r="B24" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -3472,10 +3467,10 @@
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="29" t="s">
         <v>63</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>64</v>
       </c>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -3511,7 +3506,7 @@
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28"/>
       <c r="B26" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -3546,7 +3541,7 @@
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B27" s="30"/>
       <c r="C27" s="25"/>
@@ -3582,7 +3577,7 @@
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="30"/>
       <c r="C28" s="25"/>
@@ -3618,7 +3613,7 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B29" s="30"/>
       <c r="C29" s="25"/>
@@ -3654,7 +3649,7 @@
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B30" s="30"/>
       <c r="C30" s="25"/>
@@ -3690,7 +3685,7 @@
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B31" s="30"/>
       <c r="C31" s="25"/>
@@ -3726,7 +3721,7 @@
     </row>
     <row r="32" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="32"/>
@@ -4040,7 +4035,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4286,10 +4281,10 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>46</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>47</v>
       </c>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
@@ -4327,7 +4322,7 @@
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28"/>
       <c r="B6" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
@@ -4365,7 +4360,7 @@
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="28"/>
       <c r="B7" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
@@ -4403,7 +4398,7 @@
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="28"/>
       <c r="B8" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
@@ -4441,7 +4436,7 @@
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28"/>
       <c r="B9" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
@@ -4479,7 +4474,7 @@
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28"/>
       <c r="B10" s="29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
@@ -4517,7 +4512,7 @@
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28"/>
       <c r="B11" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
@@ -4554,10 +4549,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>54</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>55</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -4595,7 +4590,7 @@
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28"/>
       <c r="B13" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
@@ -4633,7 +4628,7 @@
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28"/>
       <c r="B14" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
@@ -4670,10 +4665,10 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>58</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>59</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -4711,7 +4706,7 @@
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28"/>
       <c r="B16" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -4749,7 +4744,7 @@
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="28"/>
       <c r="B17" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
@@ -4787,7 +4782,7 @@
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="28"/>
       <c r="B18" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
@@ -4824,10 +4819,10 @@
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="29" t="s">
         <v>63</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>64</v>
       </c>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -4865,7 +4860,7 @@
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28"/>
       <c r="B20" s="29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -4902,7 +4897,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" s="30"/>
       <c r="C21" s="25"/>
@@ -4940,7 +4935,7 @@
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22" s="30"/>
       <c r="C22" s="25"/>
@@ -4978,7 +4973,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="25"/>
@@ -5016,7 +5011,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="30"/>
       <c r="C24" s="25"/>
@@ -5054,7 +5049,7 @@
     </row>
     <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="30"/>
       <c r="C25" s="25"/>
@@ -5092,7 +5087,7 @@
     </row>
     <row r="26" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="32"/>
